--- a/2026/URIARTE 630/Mayo/EXPENSAS-Mayo.xlsx
+++ b/2026/URIARTE 630/Mayo/EXPENSAS-Mayo.xlsx
@@ -1,31 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\URIARTE 630\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\URIARTE 630\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C16AA8-56A8-4F3D-8D20-3A03D8BD498A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288A70F8-6A4C-44E9-9EB4-DCD7543B329D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$122</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="74">
   <si>
     <t>UF</t>
   </si>
@@ -129,9 +134,6 @@
     <t>ARBA cuota 5</t>
   </si>
   <si>
-    <t>TARQUIRINI SABRINA</t>
-  </si>
-  <si>
     <t>RECIBO DE EXPENSAS</t>
   </si>
   <si>
@@ -213,21 +215,9 @@
     <t>Multas</t>
   </si>
   <si>
-    <t>-------</t>
-  </si>
-  <si>
-    <t>AYSA  VTO 03/02/2026</t>
-  </si>
-  <si>
-    <t>AYSA VTO 07/04/2026</t>
-  </si>
-  <si>
     <t>Subidos en Abr1l 2026</t>
   </si>
   <si>
-    <t>Recuperacion de intereses por pago fuera de termino a administracion - Desde enero 25 a dia de la fecha - Debido a que la caja inicial pertenece a la administracion</t>
-  </si>
-  <si>
     <t>Prevision ordinaria</t>
   </si>
   <si>
@@ -241,6 +231,27 @@
   </si>
   <si>
     <t>Liquidacion mes de MAYO</t>
+  </si>
+  <si>
+    <t>AYSA  VTO 05/05/2026</t>
+  </si>
+  <si>
+    <t>Gastos bancarios</t>
+  </si>
+  <si>
+    <t>Mantenimiento de cuenta bancaria</t>
+  </si>
+  <si>
+    <t>SR PROPIETARIO</t>
+  </si>
+  <si>
+    <t>Recuperacion de intereses por pago fuera de termino a administracion - Mes de Abril - Debido a que la caja inicial pertenece a la administracion</t>
+  </si>
+  <si>
+    <t>TSG - Prevision</t>
+  </si>
+  <si>
+    <t>Se solicita abonar expensas en tiempo y forma ya que de no ser asi no se pueden abonar los impuestos y servicios por falta de regularidad de pagos y la deuda se incrementara</t>
   </si>
 </sst>
 </file>
@@ -426,7 +437,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="60">
+  <borders count="58">
     <border>
       <left/>
       <right/>
@@ -1071,17 +1082,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1091,17 +1091,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1137,7 +1126,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1270,34 +1259,28 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="1" fillId="6" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="56" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1390,10 +1373,10 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1472,9 +1455,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1512,9 +1495,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1547,9 +1530,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1582,9 +1582,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1761,43 +1778,43 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G59"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:G58"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="16"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>26</v>
       </c>
@@ -1805,13 +1822,13 @@
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
       <c r="E7" s="17" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1819,12 +1836,12 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>9</v>
       </c>
@@ -1836,7 +1853,7 @@
       </c>
       <c r="F11" s="105"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="40" t="s">
         <v>31</v>
       </c>
@@ -1850,294 +1867,287 @@
         <v>20</v>
       </c>
       <c r="F12" s="30">
-        <v>-714046.60522400623</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-831053.26022400614</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="96"/>
-      <c r="C13" s="147">
+      <c r="C13" s="91">
         <v>4519.7749999999996</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="88" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F13" s="89">
         <f>'prorrateo '!F10</f>
-        <v>630000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>992505.79330000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="47" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="B14" s="96"/>
       <c r="C14" s="38">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="88" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="102">
-        <f>-C25</f>
-        <v>-645544.07499999995</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="F14" s="103">
+        <f>-C24</f>
+        <v>-570606.14500000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="96"/>
-      <c r="C15" s="100">
+      <c r="C15" s="38">
         <v>162057</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="106" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="109">
-        <v>-119176.45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+      <c r="F15" s="108">
+        <v>-31474</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="47" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B16" s="97"/>
       <c r="C16" s="91">
-        <f>16422.66</f>
-        <v>16422.66</v>
+        <v>36610.43</v>
       </c>
       <c r="E16" s="107"/>
-      <c r="F16" s="110"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F16" s="109"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="97"/>
-      <c r="C17" s="147">
-        <v>36610.43</v>
-      </c>
-      <c r="E17" s="108"/>
-      <c r="F17" s="111"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="B17" s="96"/>
+      <c r="C17" s="91">
+        <v>76048</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="88" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="145">
+        <v>-315745.03999999998</v>
+      </c>
+      <c r="G17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B18" s="96"/>
       <c r="C18" s="91">
-        <v>76048</v>
-      </c>
-      <c r="D18" s="4"/>
+        <v>0</v>
+      </c>
       <c r="E18" s="88"/>
       <c r="F18" s="90"/>
-      <c r="G18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="47" t="s">
-        <v>28</v>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="B19" s="98"/>
-      <c r="C19" s="91">
-        <v>258515.27</v>
-      </c>
-      <c r="E19" s="88"/>
-      <c r="F19" s="90"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="47" t="s">
-        <v>56</v>
+      <c r="C19" s="92">
+        <f>SUM(C12:C18)</f>
+        <v>570606.14500000002</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="32">
+        <f>SUM(F12:F17)</f>
+        <v>-756372.65192400618</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="43" t="s">
+        <v>15</v>
       </c>
       <c r="B20" s="96"/>
-      <c r="C20" s="91">
+      <c r="C20" s="93"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="102" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="96"/>
+      <c r="C21" s="93"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="96"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="39">
+        <f>SUM(C20:C22)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="88"/>
-      <c r="F20" s="90"/>
-    </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="99"/>
-      <c r="C21" s="92">
-        <f>SUM(C12:C20)</f>
-        <v>645544.07499999995</v>
-      </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="32">
-        <f>SUM(F12:F19)</f>
-        <v>-848767.13022400613</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="47"/>
-      <c r="B23" s="96"/>
-      <c r="C23" s="100"/>
       <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="39">
-        <f>SUM(C22:C23)</f>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="68">
+        <f>+C23+C19</f>
+        <v>570606.14500000002</v>
+      </c>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="37"/>
+      <c r="C25" s="69"/>
+    </row>
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="70">
         <v>0</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="68">
-        <f>+C24+C21</f>
-        <v>645544.07499999995</v>
-      </c>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="37"/>
-      <c r="C26" s="69"/>
-    </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="70">
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="34"/>
+      <c r="C27" s="45">
+        <f>SUM(C26:C26)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="45">
-        <f>SUM(C27:C27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="70">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="70">
         <f>1200000-627830.21</f>
         <v>572169.79</v>
       </c>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="101">
+        <f>C28+C24</f>
+        <v>1142775.9350000001</v>
+      </c>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="103">
-        <f>C29+C25</f>
-        <v>1217713.865</v>
-      </c>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="33" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="45">
-        <f>+C25+C28</f>
-        <v>645544.07499999995</v>
-      </c>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="36" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D36" s="5"/>
-    </row>
-    <row r="37" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="B30" s="34"/>
+      <c r="C30" s="45">
+        <f>+C24+C27</f>
+        <v>570606.14500000002</v>
+      </c>
+      <c r="E30" s="10"/>
+    </row>
+    <row r="35" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D35" s="5"/>
+    </row>
+    <row r="36" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+    </row>
+    <row r="37" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
     </row>
-    <row r="38" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-    </row>
-    <row r="39" spans="4:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D39" s="10"/>
     </row>
-    <row r="40" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D40" s="10"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="12"/>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="12"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="13"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="11"/>
       <c r="B52" s="11"/>
-      <c r="C52" s="13"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="11"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="11"/>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2155,53 +2165,53 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T121"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="14"/>
+    <col min="11" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="142" t="str">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="140" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MAYO</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
       <c r="D1" s="75"/>
       <c r="E1" s="76" t="s">
         <v>25</v>
       </c>
       <c r="F1" s="75"/>
-      <c r="G1" s="137" t="s">
+      <c r="G1" s="135" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="139"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="137"/>
       <c r="K1" s="94"/>
-      <c r="L1" s="140">
-        <f>O1-L2</f>
-        <v>941484.73</v>
-      </c>
-      <c r="M1" s="141"/>
+      <c r="L1" s="138">
+        <f>O1</f>
+        <v>570606.14500000002</v>
+      </c>
+      <c r="M1" s="139"/>
       <c r="O1" s="14">
-        <v>1200000</v>
+        <v>570606.14500000002</v>
       </c>
       <c r="P1" s="14"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="77" t="str">
         <f>'detalle y gastos'!F7</f>
         <v>Vto. 18/06</v>
@@ -2212,81 +2222,85 @@
       <c r="E2" s="41"/>
       <c r="F2" s="42"/>
       <c r="G2" s="41" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
       <c r="J2" s="67"/>
       <c r="K2" s="67"/>
-      <c r="L2" s="145">
-        <v>258515.27</v>
-      </c>
-      <c r="M2" s="146"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="123" t="s">
+      <c r="L2" s="143">
+        <f>-O2</f>
+        <v>315745.03999999998</v>
+      </c>
+      <c r="M2" s="144"/>
+      <c r="O2" s="14">
+        <v>-315745.03999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="121" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="121" t="s">
+      <c r="C3" s="119" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="121" t="s">
+      <c r="E3" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="121" t="s">
+      <c r="F3" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="121" t="s">
+      <c r="G3" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="121" t="s">
+      <c r="H3" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="125" t="s">
+      <c r="I3" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="123" t="s">
+        <v>64</v>
+      </c>
+      <c r="K3" s="119" t="s">
         <v>60</v>
       </c>
-      <c r="J3" s="125" t="s">
-        <v>69</v>
-      </c>
-      <c r="K3" s="121" t="s">
-        <v>61</v>
-      </c>
       <c r="L3" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M3" s="79" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="124"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="122"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="122"/>
+      <c r="C4" s="120"/>
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="122"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="122"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="120"/>
       <c r="L4" s="72" t="str">
         <f>A2</f>
         <v>Vto. 18/06</v>
       </c>
       <c r="M4" s="79" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="78">
         <v>1</v>
       </c>
@@ -2294,17 +2308,17 @@
         <v>0.21</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D5" s="44">
         <v>0.5</v>
       </c>
       <c r="E5" s="23">
-        <v>210000</v>
+        <v>197711.79329999999</v>
       </c>
       <c r="F5" s="38">
         <f>E5</f>
-        <v>210000</v>
+        <v>197711.79329999999</v>
       </c>
       <c r="G5" s="73">
         <f>E5-F5</f>
@@ -2316,7 +2330,7 @@
       </c>
       <c r="I5" s="23">
         <f>L$1*B5</f>
-        <v>197711.79329999999</v>
+        <v>119827.29045</v>
       </c>
       <c r="J5" s="9">
         <f>J$2*D5</f>
@@ -2325,14 +2339,14 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9">
         <f t="shared" ref="L5:L9" si="0">I5+J5+H5+G5+K5</f>
-        <v>197711.79329999999</v>
+        <v>119827.29045</v>
       </c>
       <c r="M5" s="80">
         <f>L5+L5*4%</f>
-        <v>205620.265032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>124620.38206800001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="78">
         <v>2</v>
       </c>
@@ -2340,44 +2354,44 @@
         <v>0.16</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="44">
         <v>0.5</v>
       </c>
       <c r="E6" s="23">
-        <v>172074.00727995942</v>
+        <v>378528.22389147605</v>
       </c>
       <c r="F6" s="38">
         <v>0</v>
       </c>
       <c r="G6" s="73">
         <f t="shared" ref="G6:G9" si="1">E6-F6</f>
-        <v>172074.00727995942</v>
+        <v>378528.22389147605</v>
       </c>
       <c r="H6" s="74">
         <f t="shared" ref="H6:H9" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>14454.216611516593</v>
+        <v>31796.370806883991</v>
       </c>
       <c r="I6" s="23">
         <f>L$1*B6</f>
-        <v>150637.55679999999</v>
+        <v>91296.983200000002</v>
       </c>
       <c r="J6" s="9">
         <f>L$2*B6</f>
-        <v>41362.443200000002</v>
+        <v>50519.206399999995</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9">
         <f t="shared" si="0"/>
-        <v>378528.22389147605</v>
+        <v>552140.78429836</v>
       </c>
       <c r="M6" s="80">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>393669.3528471351</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>574226.41567029443</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="78">
         <v>3</v>
       </c>
@@ -2385,42 +2399,42 @@
         <v>0.21</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" s="44"/>
       <c r="E7" s="23">
-        <v>374690.18207680772</v>
+        <v>658164.15737125953</v>
       </c>
       <c r="F7" s="38">
-        <v>0</v>
+        <v>542794</v>
       </c>
       <c r="G7" s="73">
         <f t="shared" si="1"/>
-        <v>374690.18207680772</v>
+        <v>115370.15737125953</v>
       </c>
       <c r="H7" s="74">
         <f t="shared" si="2"/>
-        <v>31473.975294451851</v>
+        <v>9691.093219185801</v>
       </c>
       <c r="I7" s="23">
         <f>L$1*B7</f>
-        <v>197711.79329999999</v>
+        <v>119827.29045</v>
       </c>
       <c r="J7" s="9">
         <f t="shared" ref="J7:J9" si="4">L$2*B7</f>
-        <v>54288.206699999995</v>
-      </c>
-      <c r="K7" s="101"/>
+        <v>66306.458399999989</v>
+      </c>
+      <c r="K7" s="100"/>
       <c r="L7" s="9">
         <f>I7+J7+H7+G7+K7</f>
-        <v>658164.15737125953</v>
+        <v>311194.99944044533</v>
       </c>
       <c r="M7" s="80">
         <f t="shared" si="3"/>
-        <v>684490.72366610996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>323642.79941806314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="78">
         <v>4</v>
       </c>
@@ -2428,15 +2442,15 @@
         <v>0.21</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="44"/>
       <c r="E8" s="23">
-        <v>210000</v>
+        <v>252000</v>
       </c>
       <c r="F8" s="38">
         <f>E8</f>
-        <v>210000</v>
+        <v>252000</v>
       </c>
       <c r="G8" s="73">
         <f t="shared" si="1"/>
@@ -2448,23 +2462,23 @@
       </c>
       <c r="I8" s="23">
         <f>L$1*B8</f>
-        <v>197711.79329999999</v>
+        <v>119827.29045</v>
       </c>
       <c r="J8" s="9">
         <f t="shared" si="4"/>
-        <v>54288.206699999995</v>
+        <v>66306.458399999989</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9">
         <f t="shared" si="0"/>
-        <v>252000</v>
+        <v>186133.74884999997</v>
       </c>
       <c r="M8" s="80">
         <f t="shared" si="3"/>
-        <v>262080</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>193579.09880399998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="78">
         <v>5</v>
       </c>
@@ -2472,43 +2486,42 @@
         <v>0.21</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="44"/>
       <c r="E9" s="23">
-        <v>210000</v>
+        <v>252000</v>
       </c>
       <c r="F9" s="38">
-        <f>E9</f>
-        <v>210000</v>
+        <v>0</v>
       </c>
       <c r="G9" s="73">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>252000</v>
       </c>
       <c r="H9" s="74">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21168</v>
       </c>
       <c r="I9" s="23">
         <f>L$1*B9</f>
-        <v>197711.79329999999</v>
+        <v>119827.29045</v>
       </c>
       <c r="J9" s="9">
         <f t="shared" si="4"/>
-        <v>54288.206699999995</v>
+        <v>66306.458399999989</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>252000</v>
+        <v>459301.74884999997</v>
       </c>
       <c r="M9" s="80">
         <f t="shared" si="3"/>
-        <v>262080</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>477673.81880399998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="81" t="s">
         <v>7</v>
       </c>
@@ -2523,80 +2536,80 @@
       </c>
       <c r="E10" s="85">
         <f>SUM(E5:E9)</f>
-        <v>1176764.1893567671</v>
+        <v>1738404.1745627355</v>
       </c>
       <c r="F10" s="85">
         <f>SUM(F5:F9)</f>
-        <v>630000</v>
+        <v>992505.79330000002</v>
       </c>
       <c r="G10" s="85">
         <f t="shared" si="5"/>
-        <v>172074.00727995942</v>
+        <v>378528.22389147605</v>
       </c>
       <c r="H10" s="85">
         <f t="shared" si="5"/>
-        <v>14454.216611516593</v>
+        <v>31796.370806883991</v>
       </c>
       <c r="I10" s="86">
         <f>SUM(I5:I9)</f>
-        <v>941484.73</v>
+        <v>570606.1449999999</v>
       </c>
       <c r="J10" s="86">
         <f>SUM(J5:J9)</f>
-        <v>204227.06329999998</v>
+        <v>249438.58159999998</v>
       </c>
       <c r="K10" s="86"/>
       <c r="L10" s="85">
         <f>SUM(L5:L9)</f>
-        <v>1738404.1745627355</v>
+        <v>1628598.5718888054</v>
       </c>
       <c r="M10" s="87">
         <f>SUM(M5:M9)</f>
-        <v>1807940.3415452451</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="144"/>
-      <c r="B11" s="144"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="144"/>
-      <c r="M11" s="144"/>
-    </row>
-    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1693742.5147643576</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="142"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="142"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="131" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="130"/>
+      <c r="E14" s="130"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
       <c r="I14" s="49"/>
       <c r="J14" s="50"/>
       <c r="K14" s="54"/>
       <c r="L14" s="54"/>
     </row>
-    <row r="15" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="133" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
+    <row r="15" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="131" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
       <c r="I15" s="51"/>
       <c r="J15" s="52"/>
       <c r="K15" s="54"/>
@@ -2608,14 +2621,14 @@
         <v>96550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C16" s="49"/>
       <c r="D16" s="53"/>
       <c r="E16" s="53"/>
       <c r="F16" s="53"/>
       <c r="G16" s="54"/>
       <c r="H16" s="54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I16" s="51"/>
       <c r="J16" s="52"/>
@@ -2628,16 +2641,16 @@
         <v>27991.75</v>
       </c>
     </row>
-    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C17" s="51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" s="54"/>
       <c r="E17" s="54"/>
       <c r="F17" s="54"/>
       <c r="G17" s="54"/>
       <c r="H17" s="54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I17" s="51"/>
       <c r="J17" s="52"/>
@@ -2650,7 +2663,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C18" s="55"/>
       <c r="D18" s="56"/>
       <c r="E18" s="56"/>
@@ -2668,21 +2681,21 @@
         <v>24923.78</v>
       </c>
     </row>
-    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="134" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="135"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="135"/>
-      <c r="G19" s="135"/>
-      <c r="H19" s="135"/>
+    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="133"/>
       <c r="I19" s="51"/>
       <c r="J19" s="52"/>
       <c r="K19" s="54"/>
       <c r="L19" s="54"/>
     </row>
-    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C20" s="51"/>
       <c r="D20" s="54"/>
       <c r="E20" s="54"/>
@@ -2700,33 +2713,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C21" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="54"/>
       <c r="E21" s="54" t="str">
         <f>C5</f>
-        <v>TARQUIRINI SABRINA</v>
+        <v>SR PROPIETARIO</v>
       </c>
       <c r="F21" s="54"/>
       <c r="G21" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="57"/>
+      <c r="I21" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="57"/>
-      <c r="I21" s="129" t="s">
-        <v>41</v>
-      </c>
-      <c r="J21" s="130"/>
+      <c r="J21" s="128"/>
       <c r="K21" s="66"/>
       <c r="L21" s="66"/>
     </row>
-    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C22" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="58" t="s">
         <v>42</v>
-      </c>
-      <c r="D22" s="58" t="s">
-        <v>43</v>
       </c>
       <c r="E22" s="54">
         <f>A5</f>
@@ -2740,21 +2753,21 @@
       <c r="K22" s="54"/>
       <c r="L22" s="54"/>
     </row>
-    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C23" s="51"/>
       <c r="D23" s="54"/>
       <c r="E23" s="54"/>
       <c r="F23" s="54"/>
       <c r="G23" s="54"/>
       <c r="H23" s="54"/>
-      <c r="I23" s="136"/>
-      <c r="J23" s="130"/>
+      <c r="I23" s="134"/>
+      <c r="J23" s="128"/>
       <c r="K23" s="66"/>
       <c r="L23" s="66"/>
     </row>
-    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C24" s="64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D24" s="54"/>
       <c r="E24" s="54"/>
@@ -2762,14 +2775,14 @@
       <c r="G24" s="54"/>
       <c r="H24" s="63">
         <f>L$1/5</f>
-        <v>188296.946</v>
+        <v>114121.22900000001</v>
       </c>
       <c r="I24" s="51"/>
       <c r="J24" s="52"/>
       <c r="K24" s="54"/>
       <c r="L24" s="54"/>
     </row>
-    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C25" s="65" t="s">
         <v>29</v>
       </c>
@@ -2786,7 +2799,7 @@
       <c r="K25" s="54"/>
       <c r="L25" s="54"/>
     </row>
-    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C26" s="65" t="s">
         <v>27</v>
       </c>
@@ -2803,7 +2816,7 @@
       <c r="K26" s="54"/>
       <c r="L26" s="54"/>
     </row>
-    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C27" s="65" t="s">
         <v>30</v>
       </c>
@@ -2820,7 +2833,7 @@
       <c r="K27" s="54"/>
       <c r="L27" s="54"/>
     </row>
-    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="65" t="s">
         <v>28</v>
       </c>
@@ -2837,7 +2850,7 @@
       <c r="K28" s="54"/>
       <c r="L28" s="54"/>
     </row>
-    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="D29" s="54"/>
       <c r="E29" s="54"/>
       <c r="F29" s="54"/>
@@ -2848,7 +2861,7 @@
       <c r="K29" s="54"/>
       <c r="L29" s="54"/>
     </row>
-    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C30" s="65" t="s">
         <v>33</v>
       </c>
@@ -2865,7 +2878,7 @@
       <c r="K30" s="54"/>
       <c r="L30" s="54"/>
     </row>
-    <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C31" s="51"/>
       <c r="D31" s="54"/>
       <c r="E31" s="54"/>
@@ -2877,71 +2890,71 @@
       <c r="K31" s="54"/>
       <c r="L31" s="54"/>
     </row>
-    <row r="32" spans="3:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="127" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="128"/>
-      <c r="E32" s="128"/>
-      <c r="F32" s="128"/>
-      <c r="G32" s="128"/>
+    <row r="32" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="125" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="126"/>
+      <c r="E32" s="126"/>
+      <c r="F32" s="126"/>
+      <c r="G32" s="126"/>
       <c r="H32" s="95">
         <f>SUM(H24:H31)</f>
-        <v>233663.3285</v>
+        <v>159487.6115</v>
       </c>
       <c r="I32" s="61"/>
       <c r="J32" s="62"/>
       <c r="K32" s="54"/>
       <c r="L32" s="54"/>
     </row>
-    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="131" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="132"/>
-      <c r="E36" s="132"/>
-      <c r="F36" s="132"/>
-      <c r="G36" s="132"/>
-      <c r="H36" s="132"/>
+    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="130"/>
+      <c r="E36" s="130"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="130"/>
+      <c r="H36" s="130"/>
       <c r="I36" s="49"/>
       <c r="J36" s="50"/>
       <c r="K36" s="54"/>
       <c r="L36" s="54"/>
     </row>
-    <row r="37" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="133" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" s="132"/>
-      <c r="E37" s="132"/>
-      <c r="F37" s="132"/>
-      <c r="G37" s="132"/>
-      <c r="H37" s="132"/>
+    <row r="37" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="131" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="130"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="130"/>
+      <c r="G37" s="130"/>
+      <c r="H37" s="130"/>
       <c r="I37" s="51"/>
       <c r="J37" s="52"/>
       <c r="K37" s="54"/>
       <c r="L37" s="54"/>
     </row>
-    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C38" s="49"/>
       <c r="D38" s="53"/>
       <c r="E38" s="53"/>
       <c r="F38" s="53"/>
       <c r="G38" s="54"/>
       <c r="H38" s="54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I38" s="51"/>
       <c r="J38" s="52"/>
       <c r="K38" s="54"/>
       <c r="L38" s="54"/>
     </row>
-    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C39" s="51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D39" s="54"/>
       <c r="E39" s="54"/>
@@ -2956,7 +2969,7 @@
       <c r="K39" s="54"/>
       <c r="L39" s="54"/>
     </row>
-    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C40" s="55"/>
       <c r="D40" s="56"/>
       <c r="E40" s="56"/>
@@ -2968,21 +2981,21 @@
       <c r="K40" s="54"/>
       <c r="L40" s="54"/>
     </row>
-    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="134" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="135"/>
-      <c r="E41" s="135"/>
-      <c r="F41" s="135"/>
-      <c r="G41" s="135"/>
-      <c r="H41" s="135"/>
+    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="133"/>
+      <c r="E41" s="133"/>
+      <c r="F41" s="133"/>
+      <c r="G41" s="133"/>
+      <c r="H41" s="133"/>
       <c r="I41" s="51"/>
       <c r="J41" s="52"/>
       <c r="K41" s="54"/>
       <c r="L41" s="54"/>
     </row>
-    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C42" s="51"/>
       <c r="D42" s="54"/>
       <c r="E42" s="54"/>
@@ -2994,9 +3007,9 @@
       <c r="K42" s="54"/>
       <c r="L42" s="54"/>
     </row>
-    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C43" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D43" s="54"/>
       <c r="E43" s="54" t="str">
@@ -3005,22 +3018,22 @@
       </c>
       <c r="F43" s="54"/>
       <c r="G43" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H43" s="57"/>
+      <c r="I43" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="H43" s="57"/>
-      <c r="I43" s="129" t="s">
-        <v>41</v>
-      </c>
-      <c r="J43" s="130"/>
+      <c r="J43" s="128"/>
       <c r="K43" s="66"/>
       <c r="L43" s="66"/>
     </row>
-    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C44" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" s="58" t="s">
         <v>42</v>
-      </c>
-      <c r="D44" s="58" t="s">
-        <v>43</v>
       </c>
       <c r="E44" s="54">
         <f>A7</f>
@@ -3034,21 +3047,21 @@
       <c r="K44" s="54"/>
       <c r="L44" s="54"/>
     </row>
-    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="51"/>
       <c r="D45" s="54"/>
       <c r="E45" s="54"/>
       <c r="F45" s="54"/>
       <c r="G45" s="54"/>
       <c r="H45" s="54"/>
-      <c r="I45" s="136"/>
-      <c r="J45" s="130"/>
+      <c r="I45" s="134"/>
+      <c r="J45" s="128"/>
       <c r="K45" s="66"/>
       <c r="L45" s="66"/>
     </row>
-    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D46" s="54"/>
       <c r="E46" s="54"/>
@@ -3056,14 +3069,14 @@
       <c r="G46" s="54"/>
       <c r="H46" s="63">
         <f>L$1/5</f>
-        <v>188296.946</v>
+        <v>114121.22900000001</v>
       </c>
       <c r="I46" s="51"/>
       <c r="J46" s="52"/>
       <c r="K46" s="54"/>
       <c r="L46" s="54"/>
     </row>
-    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="51"/>
       <c r="D47" s="54"/>
       <c r="E47" s="54"/>
@@ -3075,7 +3088,7 @@
       <c r="K47" s="54"/>
       <c r="L47" s="54"/>
     </row>
-    <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="51"/>
       <c r="D48" s="54"/>
       <c r="E48" s="54"/>
@@ -3087,70 +3100,70 @@
       <c r="K48" s="54"/>
       <c r="L48" s="54"/>
     </row>
-    <row r="49" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="127" t="s">
-        <v>44</v>
-      </c>
-      <c r="D49" s="128"/>
-      <c r="E49" s="128"/>
-      <c r="F49" s="128"/>
-      <c r="G49" s="128"/>
+    <row r="49" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="125" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="126"/>
+      <c r="E49" s="126"/>
+      <c r="F49" s="126"/>
+      <c r="G49" s="126"/>
       <c r="H49" s="95">
         <f>M6</f>
-        <v>393669.3528471351</v>
+        <v>574226.41567029443</v>
       </c>
       <c r="I49" s="61"/>
       <c r="J49" s="62"/>
       <c r="K49" s="54"/>
       <c r="L49" s="54"/>
     </row>
-    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C52" s="131" t="s">
-        <v>35</v>
-      </c>
-      <c r="D52" s="132"/>
-      <c r="E52" s="132"/>
-      <c r="F52" s="132"/>
-      <c r="G52" s="132"/>
-      <c r="H52" s="132"/>
+    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="130"/>
+      <c r="E52" s="130"/>
+      <c r="F52" s="130"/>
+      <c r="G52" s="130"/>
+      <c r="H52" s="130"/>
       <c r="I52" s="49"/>
       <c r="J52" s="50"/>
       <c r="K52" s="54"/>
       <c r="L52" s="54"/>
     </row>
-    <row r="53" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="133" t="s">
-        <v>36</v>
-      </c>
-      <c r="D53" s="132"/>
-      <c r="E53" s="132"/>
-      <c r="F53" s="132"/>
-      <c r="G53" s="132"/>
-      <c r="H53" s="132"/>
+    <row r="53" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="131" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" s="130"/>
+      <c r="E53" s="130"/>
+      <c r="F53" s="130"/>
+      <c r="G53" s="130"/>
+      <c r="H53" s="130"/>
       <c r="I53" s="51"/>
       <c r="J53" s="52"/>
       <c r="K53" s="54"/>
       <c r="L53" s="54"/>
     </row>
-    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C54" s="49"/>
       <c r="D54" s="53"/>
       <c r="E54" s="53"/>
       <c r="F54" s="53"/>
       <c r="G54" s="54"/>
       <c r="H54" s="54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I54" s="51"/>
       <c r="J54" s="52"/>
       <c r="K54" s="54"/>
       <c r="L54" s="54"/>
     </row>
-    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C55" s="51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D55" s="54"/>
       <c r="E55" s="54"/>
@@ -3165,7 +3178,7 @@
       <c r="K55" s="54"/>
       <c r="L55" s="54"/>
     </row>
-    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C56" s="55"/>
       <c r="D56" s="56"/>
       <c r="E56" s="56"/>
@@ -3177,21 +3190,21 @@
       <c r="K56" s="54"/>
       <c r="L56" s="54"/>
     </row>
-    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="134" t="s">
-        <v>38</v>
-      </c>
-      <c r="D57" s="135"/>
-      <c r="E57" s="135"/>
-      <c r="F57" s="135"/>
-      <c r="G57" s="135"/>
-      <c r="H57" s="135"/>
+    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" s="133"/>
+      <c r="E57" s="133"/>
+      <c r="F57" s="133"/>
+      <c r="G57" s="133"/>
+      <c r="H57" s="133"/>
       <c r="I57" s="51"/>
       <c r="J57" s="52"/>
       <c r="K57" s="54"/>
       <c r="L57" s="54"/>
     </row>
-    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C58" s="51"/>
       <c r="D58" s="54"/>
       <c r="E58" s="54"/>
@@ -3203,9 +3216,9 @@
       <c r="K58" s="54"/>
       <c r="L58" s="54"/>
     </row>
-    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C59" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D59" s="54"/>
       <c r="E59" s="54" t="str">
@@ -3214,22 +3227,22 @@
       </c>
       <c r="F59" s="54"/>
       <c r="G59" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59" s="57"/>
+      <c r="I59" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="H59" s="57"/>
-      <c r="I59" s="129" t="s">
-        <v>41</v>
-      </c>
-      <c r="J59" s="130"/>
+      <c r="J59" s="128"/>
       <c r="K59" s="66"/>
       <c r="L59" s="66"/>
     </row>
-    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C60" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="58" t="s">
         <v>42</v>
-      </c>
-      <c r="D60" s="58" t="s">
-        <v>43</v>
       </c>
       <c r="E60" s="54">
         <f>A6</f>
@@ -3243,21 +3256,21 @@
       <c r="K60" s="54"/>
       <c r="L60" s="54"/>
     </row>
-    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C61" s="51"/>
       <c r="D61" s="54"/>
       <c r="E61" s="54"/>
       <c r="F61" s="54"/>
       <c r="G61" s="54"/>
       <c r="H61" s="54"/>
-      <c r="I61" s="136"/>
-      <c r="J61" s="130"/>
+      <c r="I61" s="134"/>
+      <c r="J61" s="128"/>
       <c r="K61" s="66"/>
       <c r="L61" s="66"/>
     </row>
-    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C62" s="51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D62" s="54"/>
       <c r="E62" s="54"/>
@@ -3265,14 +3278,14 @@
       <c r="G62" s="54"/>
       <c r="H62" s="63">
         <f>L$1/5</f>
-        <v>188296.946</v>
+        <v>114121.22900000001</v>
       </c>
       <c r="I62" s="51"/>
       <c r="J62" s="52"/>
       <c r="K62" s="54"/>
       <c r="L62" s="54"/>
     </row>
-    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C63" s="65" t="s">
         <v>29</v>
       </c>
@@ -3289,7 +3302,7 @@
       <c r="K63" s="54"/>
       <c r="L63" s="54"/>
     </row>
-    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C64" s="65" t="s">
         <v>27</v>
       </c>
@@ -3306,7 +3319,7 @@
       <c r="K64" s="54"/>
       <c r="L64" s="54"/>
     </row>
-    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C65" s="65" t="s">
         <v>30</v>
       </c>
@@ -3323,7 +3336,7 @@
       <c r="K65" s="54"/>
       <c r="L65" s="54"/>
     </row>
-    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C66" s="65" t="s">
         <v>28</v>
       </c>
@@ -3340,7 +3353,7 @@
       <c r="K66" s="54"/>
       <c r="L66" s="54"/>
     </row>
-    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D67" s="54"/>
       <c r="E67" s="54"/>
       <c r="F67" s="54"/>
@@ -3351,7 +3364,7 @@
       <c r="K67" s="54"/>
       <c r="L67" s="54"/>
     </row>
-    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="65" t="s">
         <v>33</v>
       </c>
@@ -3368,7 +3381,7 @@
       <c r="K68" s="54"/>
       <c r="L68" s="54"/>
     </row>
-    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="51"/>
       <c r="D69" s="54"/>
       <c r="E69" s="54"/>
@@ -3380,7 +3393,7 @@
       <c r="K69" s="54"/>
       <c r="L69" s="54"/>
     </row>
-    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C70" s="51"/>
       <c r="D70" s="54"/>
       <c r="E70" s="54"/>
@@ -3392,7 +3405,7 @@
       <c r="K70" s="54"/>
       <c r="L70" s="54"/>
     </row>
-    <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C71" s="51"/>
       <c r="D71" s="54"/>
       <c r="E71" s="54"/>
@@ -3404,71 +3417,71 @@
       <c r="K71" s="54"/>
       <c r="L71" s="54"/>
     </row>
-    <row r="72" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="127" t="s">
-        <v>44</v>
-      </c>
-      <c r="D72" s="128"/>
-      <c r="E72" s="128"/>
-      <c r="F72" s="128"/>
-      <c r="G72" s="128"/>
+    <row r="72" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="125" t="s">
+        <v>43</v>
+      </c>
+      <c r="D72" s="126"/>
+      <c r="E72" s="126"/>
+      <c r="F72" s="126"/>
+      <c r="G72" s="126"/>
       <c r="H72" s="95">
         <f>SUM(H62:H71)</f>
-        <v>233663.3285</v>
+        <v>159487.6115</v>
       </c>
       <c r="I72" s="61"/>
       <c r="J72" s="62"/>
       <c r="K72" s="54"/>
       <c r="L72" s="54"/>
     </row>
-    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="131" t="s">
-        <v>35</v>
-      </c>
-      <c r="D76" s="132"/>
-      <c r="E76" s="132"/>
-      <c r="F76" s="132"/>
-      <c r="G76" s="132"/>
-      <c r="H76" s="132"/>
+    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="130"/>
+      <c r="E76" s="130"/>
+      <c r="F76" s="130"/>
+      <c r="G76" s="130"/>
+      <c r="H76" s="130"/>
       <c r="I76" s="49"/>
       <c r="J76" s="50"/>
       <c r="K76" s="54"/>
       <c r="L76" s="54"/>
     </row>
-    <row r="77" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="133" t="s">
-        <v>36</v>
-      </c>
-      <c r="D77" s="132"/>
-      <c r="E77" s="132"/>
-      <c r="F77" s="132"/>
-      <c r="G77" s="132"/>
-      <c r="H77" s="132"/>
+    <row r="77" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="131" t="s">
+        <v>35</v>
+      </c>
+      <c r="D77" s="130"/>
+      <c r="E77" s="130"/>
+      <c r="F77" s="130"/>
+      <c r="G77" s="130"/>
+      <c r="H77" s="130"/>
       <c r="I77" s="51"/>
       <c r="J77" s="52"/>
       <c r="K77" s="54"/>
       <c r="L77" s="54"/>
     </row>
-    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C78" s="49"/>
       <c r="D78" s="53"/>
       <c r="E78" s="53"/>
       <c r="F78" s="53"/>
       <c r="G78" s="54"/>
       <c r="H78" s="54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I78" s="51"/>
       <c r="J78" s="52"/>
       <c r="K78" s="54"/>
       <c r="L78" s="54"/>
     </row>
-    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C79" s="51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D79" s="54"/>
       <c r="E79" s="54"/>
@@ -3483,7 +3496,7 @@
       <c r="K79" s="54"/>
       <c r="L79" s="54"/>
     </row>
-    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C80" s="55"/>
       <c r="D80" s="56"/>
       <c r="E80" s="56"/>
@@ -3495,21 +3508,21 @@
       <c r="K80" s="54"/>
       <c r="L80" s="54"/>
     </row>
-    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="134" t="s">
-        <v>38</v>
-      </c>
-      <c r="D81" s="135"/>
-      <c r="E81" s="135"/>
-      <c r="F81" s="135"/>
-      <c r="G81" s="135"/>
-      <c r="H81" s="135"/>
+    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C81" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="D81" s="133"/>
+      <c r="E81" s="133"/>
+      <c r="F81" s="133"/>
+      <c r="G81" s="133"/>
+      <c r="H81" s="133"/>
       <c r="I81" s="51"/>
       <c r="J81" s="52"/>
       <c r="K81" s="54"/>
       <c r="L81" s="54"/>
     </row>
-    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C82" s="51"/>
       <c r="D82" s="54"/>
       <c r="E82" s="54"/>
@@ -3521,9 +3534,9 @@
       <c r="K82" s="54"/>
       <c r="L82" s="54"/>
     </row>
-    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C83" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D83" s="54"/>
       <c r="E83" s="54" t="str">
@@ -3532,22 +3545,22 @@
       </c>
       <c r="F83" s="54"/>
       <c r="G83" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H83" s="57"/>
+      <c r="I83" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="H83" s="57"/>
-      <c r="I83" s="129" t="s">
-        <v>41</v>
-      </c>
-      <c r="J83" s="130"/>
+      <c r="J83" s="128"/>
       <c r="K83" s="66"/>
       <c r="L83" s="66"/>
     </row>
-    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C84" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" s="58" t="s">
         <v>42</v>
-      </c>
-      <c r="D84" s="58" t="s">
-        <v>43</v>
       </c>
       <c r="E84" s="54">
         <f>A8</f>
@@ -3561,21 +3574,21 @@
       <c r="K84" s="54"/>
       <c r="L84" s="54"/>
     </row>
-    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C85" s="51"/>
       <c r="D85" s="54"/>
       <c r="E85" s="54"/>
       <c r="F85" s="54"/>
       <c r="G85" s="54"/>
       <c r="H85" s="54"/>
-      <c r="I85" s="136"/>
-      <c r="J85" s="130"/>
+      <c r="I85" s="134"/>
+      <c r="J85" s="128"/>
       <c r="K85" s="66"/>
       <c r="L85" s="66"/>
     </row>
-    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C86" s="51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D86" s="54"/>
       <c r="E86" s="54"/>
@@ -3583,14 +3596,14 @@
       <c r="G86" s="54"/>
       <c r="H86" s="63">
         <f>L$1/5</f>
-        <v>188296.946</v>
+        <v>114121.22900000001</v>
       </c>
       <c r="I86" s="51"/>
       <c r="J86" s="52"/>
       <c r="K86" s="54"/>
       <c r="L86" s="54"/>
     </row>
-    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C87" s="65" t="s">
         <v>29</v>
       </c>
@@ -3607,7 +3620,7 @@
       <c r="K87" s="54"/>
       <c r="L87" s="54"/>
     </row>
-    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C88" s="65" t="s">
         <v>27</v>
       </c>
@@ -3624,7 +3637,7 @@
       <c r="K88" s="54"/>
       <c r="L88" s="54"/>
     </row>
-    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C89" s="65" t="s">
         <v>30</v>
       </c>
@@ -3641,7 +3654,7 @@
       <c r="K89" s="54"/>
       <c r="L89" s="54"/>
     </row>
-    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="65" t="s">
         <v>28</v>
       </c>
@@ -3658,7 +3671,7 @@
       <c r="K90" s="54"/>
       <c r="L90" s="54"/>
     </row>
-    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D91" s="54"/>
       <c r="E91" s="54"/>
       <c r="F91" s="54"/>
@@ -3669,7 +3682,7 @@
       <c r="K91" s="54"/>
       <c r="L91" s="54"/>
     </row>
-    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C92" s="65" t="s">
         <v>33</v>
       </c>
@@ -3686,7 +3699,7 @@
       <c r="K92" s="54"/>
       <c r="L92" s="54"/>
     </row>
-    <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D93" s="54"/>
       <c r="E93" s="54"/>
       <c r="F93" s="54"/>
@@ -3697,71 +3710,71 @@
       <c r="K93" s="54"/>
       <c r="L93" s="54"/>
     </row>
-    <row r="94" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="127" t="s">
-        <v>44</v>
-      </c>
-      <c r="D94" s="128"/>
-      <c r="E94" s="128"/>
-      <c r="F94" s="128"/>
-      <c r="G94" s="128"/>
+    <row r="94" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C94" s="125" t="s">
+        <v>43</v>
+      </c>
+      <c r="D94" s="126"/>
+      <c r="E94" s="126"/>
+      <c r="F94" s="126"/>
+      <c r="G94" s="126"/>
       <c r="H94" s="95">
         <f>SUM(H86:H93)</f>
-        <v>233663.3285</v>
+        <v>159487.6115</v>
       </c>
       <c r="I94" s="61"/>
       <c r="J94" s="62"/>
       <c r="K94" s="54"/>
       <c r="L94" s="54"/>
     </row>
-    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="131" t="s">
-        <v>35</v>
-      </c>
-      <c r="D98" s="132"/>
-      <c r="E98" s="132"/>
-      <c r="F98" s="132"/>
-      <c r="G98" s="132"/>
-      <c r="H98" s="132"/>
+    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" s="130"/>
+      <c r="E98" s="130"/>
+      <c r="F98" s="130"/>
+      <c r="G98" s="130"/>
+      <c r="H98" s="130"/>
       <c r="I98" s="49"/>
       <c r="J98" s="50"/>
       <c r="K98" s="54"/>
       <c r="L98" s="54"/>
     </row>
-    <row r="99" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="133" t="s">
-        <v>36</v>
-      </c>
-      <c r="D99" s="132"/>
-      <c r="E99" s="132"/>
-      <c r="F99" s="132"/>
-      <c r="G99" s="132"/>
-      <c r="H99" s="132"/>
+    <row r="99" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C99" s="131" t="s">
+        <v>35</v>
+      </c>
+      <c r="D99" s="130"/>
+      <c r="E99" s="130"/>
+      <c r="F99" s="130"/>
+      <c r="G99" s="130"/>
+      <c r="H99" s="130"/>
       <c r="I99" s="51"/>
       <c r="J99" s="52"/>
       <c r="K99" s="54"/>
       <c r="L99" s="54"/>
     </row>
-    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C100" s="49"/>
       <c r="D100" s="53"/>
       <c r="E100" s="53"/>
       <c r="F100" s="53"/>
       <c r="G100" s="54"/>
       <c r="H100" s="54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I100" s="51"/>
       <c r="J100" s="52"/>
       <c r="K100" s="54"/>
       <c r="L100" s="54"/>
     </row>
-    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C101" s="51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D101" s="54"/>
       <c r="E101" s="54"/>
@@ -3776,7 +3789,7 @@
       <c r="K101" s="54"/>
       <c r="L101" s="54"/>
     </row>
-    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C102" s="55"/>
       <c r="D102" s="56"/>
       <c r="E102" s="56"/>
@@ -3788,21 +3801,21 @@
       <c r="K102" s="54"/>
       <c r="L102" s="54"/>
     </row>
-    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="134" t="s">
-        <v>38</v>
-      </c>
-      <c r="D103" s="135"/>
-      <c r="E103" s="135"/>
-      <c r="F103" s="135"/>
-      <c r="G103" s="135"/>
-      <c r="H103" s="135"/>
+    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="D103" s="133"/>
+      <c r="E103" s="133"/>
+      <c r="F103" s="133"/>
+      <c r="G103" s="133"/>
+      <c r="H103" s="133"/>
       <c r="I103" s="51"/>
       <c r="J103" s="52"/>
       <c r="K103" s="54"/>
       <c r="L103" s="54"/>
     </row>
-    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C104" s="51"/>
       <c r="D104" s="54"/>
       <c r="E104" s="54"/>
@@ -3814,9 +3827,9 @@
       <c r="K104" s="54"/>
       <c r="L104" s="54"/>
     </row>
-    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C105" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D105" s="54"/>
       <c r="E105" s="54" t="str">
@@ -3825,22 +3838,22 @@
       </c>
       <c r="F105" s="54"/>
       <c r="G105" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H105" s="57"/>
+      <c r="I105" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="H105" s="57"/>
-      <c r="I105" s="129" t="s">
-        <v>41</v>
-      </c>
-      <c r="J105" s="130"/>
+      <c r="J105" s="128"/>
       <c r="K105" s="66"/>
       <c r="L105" s="66"/>
     </row>
-    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C106" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="D106" s="58" t="s">
         <v>42</v>
-      </c>
-      <c r="D106" s="58" t="s">
-        <v>43</v>
       </c>
       <c r="E106" s="54">
         <v>5</v>
@@ -3853,21 +3866,21 @@
       <c r="K106" s="54"/>
       <c r="L106" s="54"/>
     </row>
-    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C107" s="51"/>
       <c r="D107" s="54"/>
       <c r="E107" s="54"/>
       <c r="F107" s="54"/>
       <c r="G107" s="54"/>
       <c r="H107" s="54"/>
-      <c r="I107" s="136"/>
-      <c r="J107" s="130"/>
+      <c r="I107" s="134"/>
+      <c r="J107" s="128"/>
       <c r="K107" s="66"/>
       <c r="L107" s="66"/>
     </row>
-    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C108" s="51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D108" s="54"/>
       <c r="E108" s="54"/>
@@ -3875,14 +3888,14 @@
       <c r="G108" s="54"/>
       <c r="H108" s="63">
         <f>L$1/5</f>
-        <v>188296.946</v>
+        <v>114121.22900000001</v>
       </c>
       <c r="I108" s="51"/>
       <c r="J108" s="52"/>
       <c r="K108" s="54"/>
       <c r="L108" s="54"/>
     </row>
-    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C109" s="65" t="s">
         <v>29</v>
       </c>
@@ -3899,7 +3912,7 @@
       <c r="K109" s="54"/>
       <c r="L109" s="54"/>
     </row>
-    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C110" s="65" t="s">
         <v>27</v>
       </c>
@@ -3916,7 +3929,7 @@
       <c r="K110" s="54"/>
       <c r="L110" s="54"/>
     </row>
-    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C111" s="65" t="s">
         <v>30</v>
       </c>
@@ -3933,7 +3946,7 @@
       <c r="K111" s="54"/>
       <c r="L111" s="54"/>
     </row>
-    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C112" s="65" t="s">
         <v>28</v>
       </c>
@@ -3950,7 +3963,7 @@
       <c r="K112" s="54"/>
       <c r="L112" s="54"/>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="D113" s="54"/>
       <c r="E113" s="54"/>
       <c r="F113" s="54"/>
@@ -3961,7 +3974,7 @@
       <c r="K113" s="54"/>
       <c r="L113" s="54"/>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C114" s="65" t="s">
         <v>33</v>
       </c>
@@ -3978,7 +3991,7 @@
       <c r="K114" s="54"/>
       <c r="L114" s="54"/>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="D115" s="54"/>
       <c r="E115" s="54"/>
       <c r="F115" s="54"/>
@@ -3989,71 +4002,71 @@
       <c r="K115" s="54"/>
       <c r="L115" s="54"/>
     </row>
-    <row r="116" spans="1:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="127" t="s">
-        <v>44</v>
-      </c>
-      <c r="D116" s="128"/>
-      <c r="E116" s="128"/>
-      <c r="F116" s="128"/>
-      <c r="G116" s="128"/>
+    <row r="116" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C116" s="125" t="s">
+        <v>43</v>
+      </c>
+      <c r="D116" s="126"/>
+      <c r="E116" s="126"/>
+      <c r="F116" s="126"/>
+      <c r="G116" s="126"/>
       <c r="H116" s="95">
         <f>SUM(H108:H115)</f>
-        <v>233663.3285</v>
+        <v>159487.6115</v>
       </c>
       <c r="I116" s="61"/>
       <c r="J116" s="62"/>
       <c r="K116" s="54"/>
       <c r="L116" s="54"/>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="112" t="s">
-        <v>62</v>
-      </c>
-      <c r="B119" s="113"/>
-      <c r="C119" s="113"/>
-      <c r="D119" s="113"/>
-      <c r="E119" s="113"/>
-      <c r="F119" s="113"/>
-      <c r="G119" s="113"/>
-      <c r="H119" s="113"/>
-      <c r="I119" s="113"/>
-      <c r="J119" s="113"/>
-      <c r="K119" s="113"/>
-      <c r="L119" s="113"/>
-      <c r="M119" s="114"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="115"/>
-      <c r="B120" s="116"/>
-      <c r="C120" s="116"/>
-      <c r="D120" s="116"/>
-      <c r="E120" s="116"/>
-      <c r="F120" s="116"/>
-      <c r="G120" s="116"/>
-      <c r="H120" s="116"/>
-      <c r="I120" s="116"/>
-      <c r="J120" s="116"/>
-      <c r="K120" s="116"/>
-      <c r="L120" s="116"/>
-      <c r="M120" s="117"/>
-    </row>
-    <row r="121" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="118"/>
-      <c r="B121" s="119"/>
-      <c r="C121" s="119"/>
-      <c r="D121" s="119"/>
-      <c r="E121" s="119"/>
-      <c r="F121" s="119"/>
-      <c r="G121" s="119"/>
-      <c r="H121" s="119"/>
-      <c r="I121" s="119"/>
-      <c r="J121" s="119"/>
-      <c r="K121" s="119"/>
-      <c r="L121" s="119"/>
-      <c r="M121" s="120"/>
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="110" t="s">
+        <v>73</v>
+      </c>
+      <c r="B119" s="111"/>
+      <c r="C119" s="111"/>
+      <c r="D119" s="111"/>
+      <c r="E119" s="111"/>
+      <c r="F119" s="111"/>
+      <c r="G119" s="111"/>
+      <c r="H119" s="111"/>
+      <c r="I119" s="111"/>
+      <c r="J119" s="111"/>
+      <c r="K119" s="111"/>
+      <c r="L119" s="111"/>
+      <c r="M119" s="112"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="113"/>
+      <c r="B120" s="114"/>
+      <c r="C120" s="114"/>
+      <c r="D120" s="114"/>
+      <c r="E120" s="114"/>
+      <c r="F120" s="114"/>
+      <c r="G120" s="114"/>
+      <c r="H120" s="114"/>
+      <c r="I120" s="114"/>
+      <c r="J120" s="114"/>
+      <c r="K120" s="114"/>
+      <c r="L120" s="114"/>
+      <c r="M120" s="115"/>
+    </row>
+    <row r="121" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="116"/>
+      <c r="B121" s="117"/>
+      <c r="C121" s="117"/>
+      <c r="D121" s="117"/>
+      <c r="E121" s="117"/>
+      <c r="F121" s="117"/>
+      <c r="G121" s="117"/>
+      <c r="H121" s="117"/>
+      <c r="I121" s="117"/>
+      <c r="J121" s="117"/>
+      <c r="K121" s="117"/>
+      <c r="L121" s="117"/>
+      <c r="M121" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="45">
